--- a/research/traditional_assets/database/data/brazil/brazil_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07665</v>
+        <v>0.1341</v>
       </c>
       <c r="E2">
-        <v>0.27415</v>
+        <v>0.358</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>147.9</v>
+        <v>268.9</v>
       </c>
       <c r="L2">
-        <v>0.2313467855466917</v>
+        <v>0.3058810146740985</v>
       </c>
       <c r="M2">
-        <v>30.3109</v>
+        <v>48.4</v>
       </c>
       <c r="N2">
-        <v>0.05965538279866167</v>
+        <v>0.05483797869929753</v>
       </c>
       <c r="O2">
-        <v>0.2049418526031102</v>
+        <v>0.1799925622908145</v>
       </c>
       <c r="P2">
-        <v>30.3109</v>
+        <v>48.4</v>
       </c>
       <c r="Q2">
-        <v>0.05965538279866167</v>
+        <v>0.05483797869929753</v>
       </c>
       <c r="R2">
-        <v>0.2049418526031102</v>
+        <v>0.1799925622908145</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>211.9</v>
+        <v>448.9</v>
       </c>
       <c r="V2">
-        <v>0.4170438889982287</v>
+        <v>0.5086109222750963</v>
       </c>
       <c r="W2">
-        <v>0.2022092610793847</v>
+        <v>0.2857711605187673</v>
       </c>
       <c r="X2">
-        <v>0.2106523743625795</v>
+        <v>0.185941419198092</v>
       </c>
       <c r="Y2">
-        <v>-0.008443113283194775</v>
+        <v>0.09982974132067535</v>
       </c>
       <c r="Z2">
-        <v>0.1682368421052632</v>
+        <v>0.2633849656949396</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06264803163143574</v>
+        <v>0.08092389382074602</v>
       </c>
       <c r="AC2">
-        <v>-0.06264803163143574</v>
+        <v>-0.08092389382074602</v>
       </c>
       <c r="AD2">
-        <v>2683.7</v>
+        <v>2931.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2683.7</v>
+        <v>2931.3</v>
       </c>
       <c r="AG2">
-        <v>2471.8</v>
+        <v>2482.4</v>
       </c>
       <c r="AH2">
-        <v>0.8408108277460994</v>
+        <v>0.7685833398883033</v>
       </c>
       <c r="AI2">
-        <v>0.7560570205093531</v>
+        <v>0.6971650097512249</v>
       </c>
       <c r="AJ2">
-        <v>0.8294909225141783</v>
+        <v>0.7377117384843982</v>
       </c>
       <c r="AK2">
-        <v>0.7405698534919255</v>
+        <v>0.660968660968661</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.101</v>
+        <v>0.212</v>
       </c>
       <c r="E3">
-        <v>0.449</v>
+        <v>0.581</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>104.3</v>
+        <v>210.7</v>
       </c>
       <c r="L3">
-        <v>0.2526035359651247</v>
+        <v>0.3347632666031141</v>
       </c>
       <c r="M3">
-        <v>14.2</v>
+        <v>37.5</v>
       </c>
       <c r="N3">
-        <v>0.06469248291571754</v>
+        <v>0.07021157086687886</v>
       </c>
       <c r="O3">
-        <v>0.1361457334611697</v>
+        <v>0.1779781680113906</v>
       </c>
       <c r="P3">
-        <v>14.2</v>
+        <v>37.5</v>
       </c>
       <c r="Q3">
-        <v>0.06469248291571754</v>
+        <v>0.07021157086687886</v>
       </c>
       <c r="R3">
-        <v>0.1361457334611697</v>
+        <v>0.1779781680113906</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>129.9</v>
+        <v>409.2</v>
       </c>
       <c r="V3">
-        <v>0.5917995444191344</v>
+        <v>0.7661486612993821</v>
       </c>
       <c r="W3">
-        <v>0.2549498900024444</v>
+        <v>0.3998102466793169</v>
       </c>
       <c r="X3">
-        <v>0.1144146607604548</v>
+        <v>0.09610247224523627</v>
       </c>
       <c r="Y3">
-        <v>0.1405352292419896</v>
+        <v>0.3037077744340806</v>
       </c>
       <c r="Z3">
-        <v>0.746249774082776</v>
+        <v>0.8124435265263973</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0624729287593016</v>
+        <v>0.0801771231429971</v>
       </c>
       <c r="AC3">
-        <v>-0.0624729287593016</v>
+        <v>-0.0801771231429971</v>
       </c>
       <c r="AD3">
-        <v>377.6</v>
+        <v>344.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>377.6</v>
+        <v>344.9</v>
       </c>
       <c r="AG3">
-        <v>247.7</v>
+        <v>-64.30000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.6323898844414672</v>
+        <v>0.3923777019340159</v>
       </c>
       <c r="AI3">
-        <v>0.4174220650011055</v>
+        <v>0.2766059828374368</v>
       </c>
       <c r="AJ3">
-        <v>0.530179794520548</v>
+        <v>-0.1368667518092806</v>
       </c>
       <c r="AK3">
-        <v>0.3197366722602298</v>
+        <v>-0.07675778918467233</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.05230000000000001</v>
+        <v>0.0562</v>
       </c>
       <c r="E4">
-        <v>0.0993</v>
+        <v>0.135</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>43.6</v>
+        <v>58.2</v>
       </c>
       <c r="L4">
-        <v>0.1925795053003534</v>
+        <v>0.2330796956347617</v>
       </c>
       <c r="M4">
-        <v>16.1109</v>
+        <v>10.9</v>
       </c>
       <c r="N4">
-        <v>0.05582432432432431</v>
+        <v>0.03127690100430416</v>
       </c>
       <c r="O4">
-        <v>0.3695160550458715</v>
+        <v>0.1872852233676976</v>
       </c>
       <c r="P4">
-        <v>16.1109</v>
+        <v>10.9</v>
       </c>
       <c r="Q4">
-        <v>0.05582432432432431</v>
+        <v>0.03127690100430416</v>
       </c>
       <c r="R4">
-        <v>0.3695160550458715</v>
+        <v>0.1872852233676976</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>82</v>
+        <v>39.7</v>
       </c>
       <c r="V4">
-        <v>0.2841302841302841</v>
+        <v>0.1139167862266858</v>
       </c>
       <c r="W4">
-        <v>0.149468632156325</v>
+        <v>0.1717320743582178</v>
       </c>
       <c r="X4">
-        <v>0.3068900879647042</v>
+        <v>0.2757803661509477</v>
       </c>
       <c r="Y4">
-        <v>-0.1574214558083792</v>
+        <v>-0.1040482917927299</v>
       </c>
       <c r="Z4">
-        <v>0.06973234361043522</v>
+        <v>0.09742489270386266</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06282313450356988</v>
+        <v>0.08167066449849494</v>
       </c>
       <c r="AC4">
-        <v>-0.06282313450356988</v>
+        <v>-0.08167066449849494</v>
       </c>
       <c r="AD4">
-        <v>2306.1</v>
+        <v>2586.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2306.1</v>
+        <v>2586.4</v>
       </c>
       <c r="AG4">
-        <v>2224.1</v>
+        <v>2546.7</v>
       </c>
       <c r="AH4">
-        <v>0.8887732685859637</v>
+        <v>0.8812566015877883</v>
       </c>
       <c r="AI4">
-        <v>0.8718714555765595</v>
+        <v>0.8744632653751225</v>
       </c>
       <c r="AJ4">
-        <v>0.8851434711664743</v>
+        <v>0.8796283503730312</v>
       </c>
       <c r="AK4">
-        <v>0.867772142021069</v>
+        <v>0.8727553118574366</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/brazil/brazil_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1341</v>
+        <v>0.09145</v>
       </c>
       <c r="E2">
-        <v>0.358</v>
+        <v>0.528</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>268.9</v>
+        <v>307</v>
       </c>
       <c r="L2">
-        <v>0.3058810146740985</v>
+        <v>0.4237405106970324</v>
       </c>
       <c r="M2">
-        <v>48.4</v>
+        <v>101.9</v>
       </c>
       <c r="N2">
-        <v>0.05483797869929753</v>
+        <v>0.05881334410712225</v>
       </c>
       <c r="O2">
-        <v>0.1799925622908145</v>
+        <v>0.3319218241042345</v>
       </c>
       <c r="P2">
-        <v>48.4</v>
+        <v>101.9</v>
       </c>
       <c r="Q2">
-        <v>0.05483797869929753</v>
+        <v>0.05881334410712225</v>
       </c>
       <c r="R2">
-        <v>0.1799925622908145</v>
+        <v>0.3319218241042345</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>448.9</v>
+        <v>288</v>
       </c>
       <c r="V2">
-        <v>0.5086109222750963</v>
+        <v>0.1662241717649775</v>
       </c>
       <c r="W2">
-        <v>0.2857711605187673</v>
+        <v>0.2238950699376494</v>
       </c>
       <c r="X2">
-        <v>0.185941419198092</v>
+        <v>0.1075643818936073</v>
       </c>
       <c r="Y2">
-        <v>0.09982974132067535</v>
+        <v>0.1163306880440421</v>
       </c>
       <c r="Z2">
-        <v>0.2633849656949396</v>
+        <v>0.1929067816918284</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08092389382074602</v>
+        <v>0.06680233397229737</v>
       </c>
       <c r="AC2">
-        <v>-0.08092389382074602</v>
+        <v>-0.06680233397229737</v>
       </c>
       <c r="AD2">
-        <v>2931.3</v>
+        <v>3132.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2931.3</v>
+        <v>3132.5</v>
       </c>
       <c r="AG2">
-        <v>2482.4</v>
+        <v>2844.5</v>
       </c>
       <c r="AH2">
-        <v>0.7685833398883033</v>
+        <v>0.6438716573143408</v>
       </c>
       <c r="AI2">
-        <v>0.6971650097512249</v>
+        <v>0.663946587537092</v>
       </c>
       <c r="AJ2">
-        <v>0.7377117384843982</v>
+        <v>0.6214633720041074</v>
       </c>
       <c r="AK2">
-        <v>0.660968660968661</v>
+        <v>0.6420993227990971</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.212</v>
+        <v>0.135</v>
       </c>
       <c r="E3">
-        <v>0.581</v>
+        <v>0.93</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>210.7</v>
+        <v>239.2</v>
       </c>
       <c r="L3">
-        <v>0.3347632666031141</v>
+        <v>0.5566674424016755</v>
       </c>
       <c r="M3">
-        <v>37.5</v>
+        <v>62.4</v>
       </c>
       <c r="N3">
-        <v>0.07021157086687886</v>
+        <v>0.05669634744684718</v>
       </c>
       <c r="O3">
-        <v>0.1779781680113906</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="P3">
-        <v>37.5</v>
+        <v>62.4</v>
       </c>
       <c r="Q3">
-        <v>0.07021157086687886</v>
+        <v>0.05669634744684718</v>
       </c>
       <c r="R3">
-        <v>0.1779781680113906</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>409.2</v>
+        <v>248.9</v>
       </c>
       <c r="V3">
-        <v>0.7661486612993821</v>
+        <v>0.226149373069235</v>
       </c>
       <c r="W3">
-        <v>0.3998102466793169</v>
+        <v>0.2651884700665189</v>
       </c>
       <c r="X3">
-        <v>0.09610247224523627</v>
+        <v>0.06693714637753431</v>
       </c>
       <c r="Y3">
-        <v>0.3037077744340806</v>
+        <v>0.1982513236889845</v>
       </c>
       <c r="Z3">
-        <v>0.8124435265263973</v>
+        <v>0.5129521308344276</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0801771231429971</v>
+        <v>0.06548001835646639</v>
       </c>
       <c r="AC3">
-        <v>-0.0801771231429971</v>
+        <v>-0.06548001835646639</v>
       </c>
       <c r="AD3">
-        <v>344.9</v>
+        <v>113.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>344.9</v>
+        <v>113.6</v>
       </c>
       <c r="AG3">
-        <v>-64.30000000000001</v>
+        <v>-135.3</v>
       </c>
       <c r="AH3">
-        <v>0.3923777019340159</v>
+        <v>0.09355954537967387</v>
       </c>
       <c r="AI3">
-        <v>0.2766059828374368</v>
+        <v>0.08893760275581304</v>
       </c>
       <c r="AJ3">
-        <v>-0.1368667518092806</v>
+        <v>-0.140163679685072</v>
       </c>
       <c r="AK3">
-        <v>-0.07675778918467233</v>
+        <v>-0.1315635939323221</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0562</v>
+        <v>0.0479</v>
       </c>
       <c r="E4">
-        <v>0.135</v>
+        <v>0.126</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>58.2</v>
+        <v>67.8</v>
       </c>
       <c r="L4">
-        <v>0.2330796956347617</v>
+        <v>0.2299864314789688</v>
       </c>
       <c r="M4">
-        <v>10.9</v>
+        <v>39.5</v>
       </c>
       <c r="N4">
-        <v>0.03127690100430416</v>
+        <v>0.0625</v>
       </c>
       <c r="O4">
-        <v>0.1872852233676976</v>
+        <v>0.5825958702064897</v>
       </c>
       <c r="P4">
-        <v>10.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q4">
-        <v>0.03127690100430416</v>
+        <v>0.0625</v>
       </c>
       <c r="R4">
-        <v>0.1872852233676976</v>
+        <v>0.5825958702064897</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>39.7</v>
+        <v>39.1</v>
       </c>
       <c r="V4">
-        <v>0.1139167862266858</v>
+        <v>0.06186708860759494</v>
       </c>
       <c r="W4">
-        <v>0.1717320743582178</v>
+        <v>0.18260166980878</v>
       </c>
       <c r="X4">
-        <v>0.2757803661509477</v>
+        <v>0.1481916174096803</v>
       </c>
       <c r="Y4">
-        <v>-0.1040482917927299</v>
+        <v>0.03441005239909967</v>
       </c>
       <c r="Z4">
-        <v>0.09742489270386266</v>
+        <v>0.101028101439342</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08167066449849494</v>
+        <v>0.06812464958812835</v>
       </c>
       <c r="AC4">
-        <v>-0.08167066449849494</v>
+        <v>-0.06812464958812835</v>
       </c>
       <c r="AD4">
-        <v>2586.4</v>
+        <v>3018.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2586.4</v>
+        <v>3018.9</v>
       </c>
       <c r="AG4">
-        <v>2546.7</v>
+        <v>2979.8</v>
       </c>
       <c r="AH4">
-        <v>0.8812566015877883</v>
+        <v>0.8268919992330658</v>
       </c>
       <c r="AI4">
-        <v>0.8744632653751225</v>
+        <v>0.8774086668410498</v>
       </c>
       <c r="AJ4">
-        <v>0.8796283503730312</v>
+        <v>0.8250179965668089</v>
       </c>
       <c r="AK4">
-        <v>0.8727553118574366</v>
+        <v>0.8759995296331138</v>
       </c>
       <c r="AL4">
         <v>0</v>
